--- a/results/Int All Data -0.2/Rando_8_permute.xlsx
+++ b/results/Int All Data -0.2/Rando_8_permute.xlsx
@@ -440,527 +440,527 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8182136537548577</v>
+        <v>0.8072439639497639</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8276796084987887</v>
+        <v>0.8063538259748594</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8270247296513755</v>
+        <v>0.805217873876714</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8281914085149262</v>
+        <v>0.799906834570848</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8285495747040379</v>
+        <v>0.8012165922656744</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8281914085149262</v>
+        <v>0.8050642400496882</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8238934142455852</v>
+        <v>0.8079910230933924</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8115621299887601</v>
+        <v>0.8079910230933924</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8129333412143969</v>
+        <v>0.807274690715169</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8202090170625025</v>
+        <v>0.8080419216284529</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8201782902970973</v>
+        <v>0.8080419216284529</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8141614736087577</v>
+        <v>0.8100065581706926</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8217136903455096</v>
+        <v>0.8119404679475271</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.821979676238406</v>
+        <v>0.8112548623347087</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8204653861814935</v>
+        <v>0.8112241355693036</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8204653861814935</v>
+        <v>0.8066908821724714</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8172418904794876</v>
+        <v>0.8070490483615832</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8151745186452828</v>
+        <v>0.8052380456463691</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8183365608164782</v>
+        <v>0.8045217132681457</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8187254537709951</v>
+        <v>0.8036315752932413</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8187561805364002</v>
+        <v>0.8036315752932413</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8184287411126936</v>
+        <v>0.8007662457803473</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8156959354353255</v>
+        <v>0.8073150342544795</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8037544823548618</v>
+        <v>0.8073457610198846</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.801544031689381</v>
+        <v>0.8139051044897668</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8016669387510016</v>
+        <v>0.8054224062388</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7732066827665536</v>
+        <v>0.8105798117176403</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7724596236229249</v>
+        <v>0.8016563837552517</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7713236715247793</v>
+        <v>0.8020145499443634</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7809125333303311</v>
+        <v>0.7990570401352541</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7740459222063976</v>
+        <v>0.7990570401352541</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7729714236390623</v>
+        <v>0.7957211923673777</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7761027390448526</v>
+        <v>0.7953015726474557</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7750282404775174</v>
+        <v>0.7903688713003567</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.773677201021536</v>
+        <v>0.7784466517677038</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7728072348162868</v>
+        <v>0.7809230883260809</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7711700376977537</v>
+        <v>0.7818132263009854</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7814445051161237</v>
+        <v>0.780708000968245</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7784869953070144</v>
+        <v>0.780708000968245</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.785803952916275</v>
+        <v>0.7799916685900214</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7796440573966597</v>
+        <v>0.7755813222548098</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7825093869095536</v>
+        <v>0.7762976546330334</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7871962741334113</v>
+        <v>0.7696355758711859</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7881488038609705</v>
+        <v>0.7607428746742024</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.77362724070832</v>
+        <v>0.7554318353683365</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7718364097627612</v>
+        <v>0.7506633228440132</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7668528098806018</v>
+        <v>0.7415151907498831</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7695030520356599</v>
+        <v>0.7337478866552954</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7698612182247717</v>
+        <v>0.7303602021305142</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7709357167921069</v>
+        <v>0.7303602021305142</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7673233281355842</v>
+        <v>0.7392529033274976</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7739854068974317</v>
+        <v>0.7431725596380715</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7779348517515663</v>
+        <v>0.7437352581892693</v>
       </c>
     </row>
     <row r="55">
@@ -970,1017 +970,1017 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7740363054324921</v>
+        <v>0.7450450158840958</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.771140249154193</v>
+        <v>0.7445024891025532</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7728696265689414</v>
+        <v>0.7393959821587734</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7800838488862368</v>
+        <v>0.7388438386033254</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7867862711873947</v>
+        <v>0.7388438386033254</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7864588317636882</v>
+        <v>0.7367562949994653</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7981150654034448</v>
+        <v>0.7287028332423258</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7947072091090082</v>
+        <v>0.7287537317773862</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7938055779165095</v>
+        <v>0.7225016559615554</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7931506990690963</v>
+        <v>0.7176198531495169</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7732364713101143</v>
+        <v>0.7073655575008022</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7803172315700393</v>
+        <v>0.6975827183289143</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7709751221095731</v>
+        <v>0.6975827183289143</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7751396543215436</v>
+        <v>0.689805797460421</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7777793414808518</v>
+        <v>0.6579482401772865</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7829569187293475</v>
+        <v>0.5786581738825309</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7784543920979203</v>
+        <v>0.5984802213452975</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7980920789682562</v>
+        <v>0.5981326101519356</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7898129748575311</v>
+        <v>0.6286890882923049</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7754661555234058</v>
+        <v>0.6303771839458984</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7700322091559193</v>
+        <v>0.6300190177567866</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7700322091559193</v>
+        <v>0.625393584063739</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7683441135023259</v>
+        <v>0.6128577674448279</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7679859473132141</v>
+        <v>0.6173093955411946</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7727966798205369</v>
+        <v>0.6117525421120875</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7778820767728171</v>
+        <v>0.6092146520229</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7669431137331284</v>
+        <v>0.5984783449016087</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7670554657989992</v>
+        <v>0.5887051225036263</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.761928787085564</v>
+        <v>0.5866790324305763</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7355051761699157</v>
+        <v>0.5858810747518872</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7505894378737641</v>
+        <v>0.5929426014640014</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7542843900525967</v>
+        <v>0.5917759226004508</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7542843900525967</v>
+        <v>0.5883066127752039</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.753086984423641</v>
+        <v>0.5946719788787498</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7493833536927474</v>
+        <v>0.593270040887708</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7388832439207915</v>
+        <v>0.5874164748002995</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7356088496837254</v>
+        <v>0.5874164748002995</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7220609262501336</v>
+        <v>0.5874164748002995</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7315364977679701</v>
+        <v>0.5820123169763737</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7278828273502926</v>
+        <v>0.58640249154193</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7265634528815608</v>
+        <v>0.5781848409620152</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7265634528815608</v>
+        <v>0.5634404501213121</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7194798779561025</v>
+        <v>0.5368420953871385</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6946118388585218</v>
+        <v>0.5566967460589991</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6732457127952819</v>
+        <v>0.5374566306952412</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6519928770197572</v>
+        <v>0.5376102645222668</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6376066523681658</v>
+        <v>0.5372828250985602</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6287350611626821</v>
+        <v>0.5070345528340867</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6396020156758107</v>
+        <v>0.5074234457886035</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6383844382771995</v>
+        <v>0.5051409865965627</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6300314491962253</v>
+        <v>0.506215485163898</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6293967421184674</v>
+        <v>0.506215485163898</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6274013788108226</v>
+        <v>0.4981610851849141</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6109775708685871</v>
+        <v>0.4884185895523369</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6082764301784686</v>
+        <v>0.488275510721061</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6231235563111369</v>
+        <v>0.4857174488622183</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6231235563111369</v>
+        <v>0.4852258206157363</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5444663206504504</v>
+        <v>0.4809374431203007</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5377629601274481</v>
+        <v>0.4908729778973698</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5415587711545571</v>
+        <v>0.4941166453690308</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.540719531714713</v>
+        <v>0.4971144987174507</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5180628815044575</v>
+        <v>0.4971144987174507</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5163229490939591</v>
+        <v>0.4970837719520456</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5155144364195202</v>
+        <v>0.4970837719520456</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5148288308067019</v>
+        <v>0.4963981663392272</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.517305267365079</v>
+        <v>0.4974726649065625</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5230464813866168</v>
+        <v>0.4964288931046324</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5164458561555797</v>
+        <v>0.4971452254828559</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5346412614955631</v>
+        <v>0.4967870592937441</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5346412614955631</v>
+        <v>0.4987516958359838</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5314283207893072</v>
+        <v>0.4988131493667941</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5317557602130139</v>
+        <v>0.4992942226175264</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5538497118720715</v>
+        <v>0.5003994479502667</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5526014077080553</v>
+        <v>0.5003994479502667</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5526014077080553</v>
+        <v>0.5011157803284902</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.544456703876545</v>
+        <v>0.5011157803284902</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.543024039120098</v>
+        <v>0.4989466114241645</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5401078110721437</v>
+        <v>0.5004916282464822</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5403536251953847</v>
+        <v>0.501473946517602</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5414780840759359</v>
+        <v>0.5040934619072549</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4903168468990829</v>
+        <v>0.5034078562944365</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4858835141286827</v>
+        <v>0.5044209013309615</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4919397361344884</v>
+        <v>0.4996725605762934</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4995928117195167</v>
+        <v>0.4996725605762934</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.505672020160511</v>
+        <v>0.4990176817288802</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5058045439960369</v>
+        <v>0.4990176817288802</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5041875186471592</v>
+        <v>0.4990176817288802</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5041875186471592</v>
+        <v>0.4990176817288802</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5071844337737347</v>
+        <v>0.4990176817288802</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5028163074215224</v>
+        <v>0.5000921802962154</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5033069974461601</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5064277578562006</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5035317015779015</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4991924255474056</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4987420790620784</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4987420790620784</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4997243973331982</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5026713521465578</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5010034282626196</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4991098620250956</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4996725605762934</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4996725605762934</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
   </sheetData>
